--- a/Statistics_/Section 5 - Hypothesis testing_/7_Test for the mean. Population variance unknown/Course notes/Test for the mean. Population variance unknown.xlsx
+++ b/Statistics_/Section 5 - Hypothesis testing_/7_Test for the mean. Population variance unknown/Course notes/Test for the mean. Population variance unknown.xlsx
@@ -1,30 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya Valchanov\Desktop\Statistics for Data Science and Business Analysis\Filming\REBOOT\Excel Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics_\Section 5 - Hypothesis testing_\7_Test for the mean. Population variance unknown\Course notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F02CFE-5A12-4652-AAF9-49124879A38B}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE811CA8-7C19-45BF-902A-08A1ACD1DE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5652" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Open rate dataset" sheetId="1" r:id="rId1"/>
     <sheet name="More data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -163,10 +161,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -275,7 +273,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -294,8 +292,8 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
@@ -303,13 +301,13 @@
     <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -341,6 +339,287 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F74C8AD7-EA83-4644-B05A-FA6E1088AC6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="527050" y="2501900"/>
+          <a:ext cx="4565650" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB"/>
+            <a:t>A </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="1"/>
+            <a:t>t-score</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB"/>
+            <a:t> (also called a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="1"/>
+            <a:t>t-statistic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB"/>
+            <a:t>) tells you how far your sample’s average is from the expected population average, measured in units of standard error.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>161731</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>72890</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{676AD6C0-3059-4382-BA44-11861F6EABAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5308600" y="2495550"/>
+          <a:ext cx="1552381" cy="1076190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E0AD36D-6129-4D47-B564-1AD4FDC21B5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="495300" y="3365500"/>
+          <a:ext cx="4667250" cy="1231900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>The data</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> shows that the sample mean is only around (-0.53) standard deviations from the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>hypothesized</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> mean. Furthermore, since the the p-value (2-sided) is greater than 0.005 so we fail to reject the null hypothesis and conclude that the average opening rate is 40% (our Null hypothesis). Another view is that the test statistic is not in the critical zone of the criticl value of +-2.26 so the Null hypothesis is not rejected</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>520991</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>50801</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60711BE5-E05E-43F8-959E-F86C66D89A07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="355600" y="5124451"/>
+          <a:ext cx="7474241" cy="1784350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -833,11 +1112,12 @@
       <c r="J35" s="14"/>
     </row>
   </sheetData>
-  <sortState ref="B22:I41">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:I41">
     <sortCondition descending="1" ref="I41"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
